--- a/output/pdf_financials_xlsx/VIZ.xlsx
+++ b/output/pdf_financials_xlsx/VIZ.xlsx
@@ -1826,34 +1826,34 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.001453</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.001612</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.213693</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.005537</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.029723</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.018536</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>3.19119</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.676889</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.656818</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.13194</v>
       </c>
       <c r="L34" s="1" t="inlineStr">
         <is>
@@ -1910,34 +1910,34 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.001453</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.001612</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.213693</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.005537</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.029723</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.018536</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>3.19119</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.676889</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.656818</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.13194</v>
       </c>
       <c r="L36" s="1" t="inlineStr">
         <is>
@@ -2414,34 +2414,34 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.035288</v>
+        <v>0.033835</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.033456</v>
+        <v>0.031844</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.247931</v>
+        <v>0.034238</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.042027</v>
+        <v>0.03649</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.038357</v>
+        <v>0.008633999999999999</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.021365</v>
+        <v>0.002829</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>3.236178</v>
+        <v>0.044988</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.876939</v>
+        <v>0.20005</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.773798</v>
+        <v>0.11698</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.245165</v>
+        <v>0.113225</v>
       </c>
       <c r="L48" s="1" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">
@@ -15779,7 +15779,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">

--- a/output/pdf_financials_xlsx/VIZ.xlsx
+++ b/output/pdf_financials_xlsx/VIZ.xlsx
@@ -3235,31 +3235,31 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.063</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.01686</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.038436</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.099856</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.173568</v>
       </c>
       <c r="H67" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.074576</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.022323</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="L67" s="1" t="inlineStr">
         <is>
@@ -5023,13 +5023,13 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.002014</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.00174</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.001177</v>
       </c>
       <c r="E110" s="3" t="n">
         <v>0</v>
@@ -14229,7 +14229,11 @@
           <t>Accretion 7</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>
@@ -15016,7 +15020,11 @@
           <t>Accretion 6</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E129" s="5" t="n">
         <v>0.002014</v>
       </c>
